--- a/www/download/COUNTRY.JPN.rpA2.xlsx
+++ b/www/download/COUNTRY.JPN.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Japão</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>93.4579392724969</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>108.69565009423</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>120.772951100123</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.992</t>
+          <t>130.378093106072</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>113.895220219769</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>107.758622330519</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>121.359218118173</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>125.156448030675</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>115.740744752688</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>108.108106778803</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>110.011003151538</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>116.279065778384</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>117.647052871306</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>103.094909107448</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.822</t>
+          <t>93.454450428309</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>66.858</t>
+          <t>1.74748381675217</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>66.907</t>
+          <t>2.04100335940344</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.374</t>
+          <t>2.36320475722598</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>2.39842258552192</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>65.664</t>
+          <t>2.17438111001415</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>65.253</t>
+          <t>2.05414089043411</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>2.05088070163176</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>63.748</t>
+          <t>2.09011929439924</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>63.537</t>
+          <t>2.08391801908618</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>63.677</t>
+          <t>1.89979974182728</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>63.917</t>
+          <t>1.88936301241197</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>64.197</t>
+          <t>2.01916734903094</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>64.438</t>
+          <t>2.26504274392392</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>63.045</t>
+          <t>2.23908952614129</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>58.129</t>
+          <t>2.04266808781349</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>53.767</t>
+          <t>0.836332461418831</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.252</t>
+          <t>1.03457087898697</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>54.767</t>
+          <t>1.22080379682726</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>54.304</t>
+          <t>1.25449883004651</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>53.699</t>
+          <t>1.0858216552075</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>53.778</t>
+          <t>0.981987206069746</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>0.995972005358446</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53.22</t>
+          <t>1.07163584787874</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>53.165</t>
+          <t>1.01688072447606</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>53.333</t>
+          <t>0.930485524012193</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>53.676</t>
+          <t>0.913984309489264</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>54.501</t>
+          <t>0.989142717340987</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>54.736</t>
+          <t>1.1437806422936</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>53.523</t>
+          <t>1.13324575885986</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>49.344</t>
+          <t>1.01573830833141</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>128222.472</t>
+          <t>-0.199296490936569</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>128765.062</t>
+          <t>-0.107813197266307</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>127817.187</t>
+          <t>-0.0357708956363005</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>124807.729</t>
+          <t>-0.0265261359209589</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>121678.753</t>
+          <t>-0.101044236692951</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>121538.02</t>
+          <t>-0.154670651824948</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120328.064</t>
+          <t>-0.143072783857889</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>117808.29</t>
+          <t>-0.100225705312589</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>117674.143</t>
+          <t>-0.131873694719184</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>117553.502</t>
+          <t>-0.160763317780841</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>115915.217</t>
+          <t>-0.155368280676693</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>117204.754</t>
+          <t>-0.115952302898118</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>117623.105</t>
+          <t>-0.048428693044882</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>114963.431</t>
+          <t>-0.0520169310743733</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>105856.42</t>
+          <t>-0.0992608012756044</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>102785.336</t>
+          <t>486961012221.928</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>103927.218</t>
+          <t>474231768345.392</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>103369.217</t>
+          <t>464386198486.888</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>101246.989</t>
+          <t>430875499561.185</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>99076.807</t>
+          <t>443444695212.143</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>100177.904</t>
+          <t>465698264420.366</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>99460.607</t>
+          <t>456301842737.461</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>97626.584</t>
+          <t>441150724422.561</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>97944.352</t>
+          <t>456708661971.555</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>98147.153</t>
+          <t>478111746221.291</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>96831.355</t>
+          <t>480322868576.713</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>99350.695</t>
+          <t>494629856978.257</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>99761.612</t>
+          <t>491659498693.413</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>97421.377</t>
+          <t>510624054234.399</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>89716.478</t>
+          <t>439070105111.013</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>157242594157.723</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.83</t>
+          <t>144063478831.121</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>131512900295.288</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>127875974853.143</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.63</t>
+          <t>135502753433.811</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26.09</t>
+          <t>144432419446.196</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>143535479902.654</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>137423750551.397</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>141230214978.218</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>149285336029.248</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>148647784723.307</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>146452754338.144</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>136295829274.194</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>133850966907.608</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>130875074667.642</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>2129630.52088187</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>58.61</t>
+          <t>2365007.8767138</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.04</t>
+          <t>2530428.45410966</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>59.19</t>
+          <t>2626245.30086201</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>2488121.91617994</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>59.81</t>
+          <t>2441244.92023475</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>59.86</t>
+          <t>2779059.38760109</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>59.19</t>
+          <t>2848192.0419619</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>2732099.16110322</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.66</t>
+          <t>2599047.65954383</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2583393.1144601</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2724308.63108703</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2608893.63559279</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2359288.12276846</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>2203245.92328761</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>832119.143911919</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>837929.917429277</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>827308.734268327</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>796846.532387312</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.97</t>
+          <t>810701.977507947</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>821278.730255562</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>789074.702561017</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>9.42</t>
+          <t>783425.481074982</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>845475.164310668</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>918702.640226192</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>964016.640654745</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1009300.70892011</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1133506.32563501</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1196777.00727118</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>1024195.49502359</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>2124196.65238359</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>2062352.47989845</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.82</t>
+          <t>1986243.22800134</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>1820198.34305419</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>1932753.70321303</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>2041323.81122767</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>1929443.24215544</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>1889358.39252717</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>2094198.37231522</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>2377818.50152718</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>2540897.08784907</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>2723301.23046373</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>3034586.21703312</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>3442849.39434147</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>2736307.1767071</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>0.984823255892516</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>1.21637486524701</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>54.64</t>
+          <t>1.4467433604077</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>1.50396060207041</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>53.73</t>
+          <t>1.34103003578273</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>1.25336717884525</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.89</t>
+          <t>1.28536183629686</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>1.3673023298218</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>52.23</t>
+          <t>1.34637813478269</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>1.24067039969177</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>1.23602588757475</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>1.33078426118789</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>1.5156254835241</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>1.49961980160608</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>1.36085403244736</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>1238577.27673467</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1135587.3850905</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>1055483.71619686</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>992382.890236023</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>1182799.27149798</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>1310499.49508807</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>1202462.87013806</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>1148355.30447645</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1255511.94484904</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>1361019.55503367</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1386771.57974616</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1361629.24965676</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1401105.22131454</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1684818.85989241</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>1822179.78509325</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>93.4579392724969</t>
+          <t>2924.53995480246</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>108.69565009423</t>
+          <t>2655.47062207836</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>120.772951100123</t>
+          <t>2401.32519678724</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>130.378093106072</t>
+          <t>2354.83490048384</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>113.895220219769</t>
+          <t>2523.39210617679</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>107.758622330519</t>
+          <t>2685.70527438204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>121.359218118173</t>
+          <t>2667.93697053834</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>125.156448030675</t>
+          <t>2582.17753138436</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>115.740744752688</t>
+          <t>2656.46248786345</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>108.108106778803</t>
+          <t>2799.09336805473</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>110.011003151538</t>
+          <t>2769.35002841595</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>116.279065778384</t>
+          <t>2687.15792746958</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>117.647052871306</t>
+          <t>2490.05131710688</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>103.094909107448</t>
+          <t>2500.82175366355</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>93.454450428309</t>
+          <t>2652.31567718666</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.745</t>
+          <t>179091984666.001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>151823486124.231</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>135538993172.52</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>130481635687.687</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.207</t>
+          <t>145826001960.376</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>163941499184.074</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>146660092921.162</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.957</t>
+          <t>146602982423.495</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.093</t>
+          <t>160727819940.687</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.273</t>
+          <t>179178515446.452</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>172477401262.397</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>159824482536.12</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2.184</t>
+          <t>142464955903.59</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2.427</t>
+          <t>132727598717.847</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>124439980661.919</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.161</t>
+          <t>172602958699.491</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.706</t>
+          <t>147577578208.061</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>130630195450.207</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>126626521591.45</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.523</t>
+          <t>141102425509.526</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.676</t>
+          <t>154984748133.921</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.342</t>
+          <t>142000963595.115</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>141974394750.182</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.363</t>
+          <t>150533228710.27</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.558</t>
+          <t>166658657651.135</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.537</t>
+          <t>158726163951.378</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.438</t>
+          <t>147843037403.656</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2.439</t>
+          <t>131461330681.119</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>122868811714.883</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.756</t>
+          <t>115639458130.042</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21.289</t>
+          <t>6489025966.50999</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18.315</t>
+          <t>4245907916.17</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>16.234</t>
+          <t>4908797722.31294</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>14.762</t>
+          <t>3855114096.2369</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>16.629</t>
+          <t>4723576450.8502</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>8956751050.15266</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>14.986</t>
+          <t>4659129326.0478</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14.368</t>
+          <t>4628587673.31269</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>15.445</t>
+          <t>10194591230.4172</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16.527</t>
+          <t>12519857795.3174</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>16.431</t>
+          <t>13751237311.0191</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>15.696</t>
+          <t>11981445132.4632</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>11003625222.4709</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>18.261</t>
+          <t>9858787002.96419</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>19.296</t>
+          <t>8800522531.87698</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9.871</t>
+          <t>5804.69491507878</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.653</t>
+          <t>5885.51834217631</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7.989</t>
+          <t>5875.42648141888</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7.179</t>
+          <t>5896.41381519194</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8.074</t>
+          <t>5907.33671261693</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>6051.88011734407</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7.611</t>
+          <t>6097.20133411377</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7.256</t>
+          <t>6112.7948860597</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7.844</t>
+          <t>6233.06549739322</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.568</t>
+          <t>6271.84565577378</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8.632</t>
+          <t>6192.33835529393</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8.377</t>
+          <t>6263.18540467239</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8.489</t>
+          <t>6264.03654859681</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>9.696</t>
+          <t>6251.10357574465</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9.388</t>
+          <t>6261.73016180949</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5724.48236675617</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.607</t>
+          <t>5818.31712158105</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>5813.48899718964</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>5837.12954714243</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.353</t>
+          <t>5846.83145691499</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.637</t>
+          <t>5975.63076286651</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.048</t>
+          <t>6054.81654892029</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3.886</t>
+          <t>6083.6908715315</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>6193.68038906768</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4.555</t>
+          <t>6219.86900365406</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4.528</t>
+          <t>6150.73041045164</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4.309</t>
+          <t>6201.74392698894</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>4.311</t>
+          <t>6202.99986153109</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>4.786</t>
+          <t>6192.17380600655</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>4.915</t>
+          <t>6198.78203340088</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>174.75</t>
+          <t>483962.022809018</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>204.1</t>
+          <t>455957.578364688</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>236.32</t>
+          <t>464289.436779155</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>239.84</t>
+          <t>422241.077273735</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>217.44</t>
+          <t>449039.96309977</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>205.41</t>
+          <t>512774.676338099</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>205.09</t>
+          <t>433152.032599372</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>209.01</t>
+          <t>446074.530739801</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>208.39</t>
+          <t>508743.94452293</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>189.98</t>
+          <t>613148.226897316</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>188.94</t>
+          <t>653686.58796679</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>201.92</t>
+          <t>703104.29234662</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>226.5</t>
+          <t>772058.453217856</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>223.91</t>
+          <t>861051.099931609</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>204.27</t>
+          <t>640035.862377991</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>83.63</t>
+          <t>30307127278.8192</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>103.46</t>
+          <t>31021594735.6164</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>122.08</t>
+          <t>33813504342.9026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>125.45</t>
+          <t>32768156081.3615</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>108.58</t>
+          <t>33230665001.0035</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>36585934462.513</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>36456679007.4977</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>107.16</t>
+          <t>38185712110.0061</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>101.69</t>
+          <t>40139708025.993</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>93.05</t>
+          <t>45863483881.0154</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>48489278274.9568</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>98.91</t>
+          <t>54438972961.0889</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>114.38</t>
+          <t>58018575626.7145</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>113.32</t>
+          <t>60349072791.8129</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>101.57</t>
+          <t>42479723559.8772</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-19.93</t>
+          <t>361449.028162005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>378258.286699501</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>364293.55567603</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>305787.918290855</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>332977.695824036</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-15.47</t>
+          <t>393855.253197297</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>364150.906360956</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>353103.882198101</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>393676.23411606</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>467719.977847277</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>530733.092738067</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>591311.642769675</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>639123.642918831</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>782839.984506907</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>569068.802394461</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>382726.006</t>
+          <t>174167138716.371</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>389284.549</t>
+          <t>160975887955.532</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>391676.126</t>
+          <t>143175025772.142</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>388633.926</t>
+          <t>130805481497.718</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>383923.988</t>
+          <t>145476360455.585</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>389925.328</t>
+          <t>165371863291.066</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>392107.376</t>
+          <t>161506225818.889</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>387820.54</t>
+          <t>155722245707.583</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>393525.192</t>
+          <t>166796837764.534</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>396059.821</t>
+          <t>185118035495.711</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>393133.472</t>
+          <t>189529675637.643</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>398136.071</t>
+          <t>187994244348.253</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>399710.537</t>
+          <t>172751081457.137</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>390385.671</t>
+          <t>178319530024.493</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>360330.389</t>
+          <t>151987397466.754</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>312098.758</t>
+          <t>122512.994647013</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>319298.673</t>
+          <t>77699.2916651878</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>321778.316</t>
+          <t>99995.8811031255</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>320196.403</t>
+          <t>116453.158982879</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>317216.016</t>
+          <t>116062.267275734</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>325459.274</t>
+          <t>118919.423140802</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>328030.508</t>
+          <t>69001.1262384158</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>325323.565</t>
+          <t>92970.6485417003</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>331379.488</t>
+          <t>115067.71040687</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>334499.234</t>
+          <t>145428.24905004</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>332380.295</t>
+          <t>122953.495228723</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>341349.775</t>
+          <t>111792.649576946</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>342869.261</t>
+          <t>132934.810299025</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>334576.527</t>
+          <t>78211.1154247029</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>308976.948</t>
+          <t>70967.05998353</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>486961.012</t>
+          <t>-143860011437.551</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>474231.768</t>
+          <t>-129954293219.915</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>464386.198</t>
+          <t>-109361521429.239</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>430875.5</t>
+          <t>-98037325416.356</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>443444.695</t>
+          <t>-112245695454.581</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>465698.264</t>
+          <t>-128785928828.553</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>456301.843</t>
+          <t>-125049546811.392</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>441150.724</t>
+          <t>-117536533597.577</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>456708.662</t>
+          <t>-126657129738.541</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>478111.746</t>
+          <t>-139254551614.695</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>480322.869</t>
+          <t>-141040397362.686</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>494629.857</t>
+          <t>-133555271387.164</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>491659.499</t>
+          <t>-114732505830.423</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>510624.054</t>
+          <t>-117970457232.68</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>439070.105</t>
+          <t>-109507673906.877</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.124</t>
+          <t>2469602.19314</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.062</t>
+          <t>2150162.69387</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>1958081.07133</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1762337.40213</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>1976049.10429</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.041</t>
+          <t>2070706.36648</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>1760254.25355</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.889</t>
+          <t>1666078.9694</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.094</t>
+          <t>1800835.6686</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>1964591.70782</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.541</t>
+          <t>1935959.52168</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.723</t>
+          <t>1824377.36754</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>3.035</t>
+          <t>1827858.90132</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.443</t>
+          <t>1965124.84046</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.736</t>
+          <t>1988539.81573</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>190758.977</t>
+          <t>0.0394434673608987</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>192679.472</t>
+          <t>0.0418010038489623</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>193425.837</t>
+          <t>0.0430304205892913</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>188628.7</t>
+          <t>0.0409042669490046</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>186004.813</t>
+          <t>0.0389487529557792</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>187362.768</t>
+          <t>0.0379092855945517</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>186611.471</t>
+          <t>0.0336576202573701</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>182923.854</t>
+          <t>0.0366244713755246</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>184383.598</t>
+          <t>0.0376119565346933</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>184725</t>
+          <t>0.0384392310000728</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>182234.55</t>
+          <t>0.0368109342702985</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>183318.048</t>
+          <t>0.0324893574469158</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>183649.141</t>
+          <t>0.0300305437030943</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>177499.233</t>
+          <t>0.0211981156577775</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>164343.253</t>
+          <t>0.0172100433782819</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>2745397.56350226</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>2356418.57498836</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>2155235.27917576</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>1967747.36004907</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>2207154.36040258</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>2355518.11130577</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>2070012.8644661</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>1956912.12619623</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>2092714.68105092</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>2272852.69144693</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.964</t>
+          <t>2250071.87505063</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>2181417.80457924</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>2184132.6284078</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.197</t>
+          <t>2427079.55996368</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.024</t>
+          <t>2467893.18097585</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>157242.594</t>
+          <t>3161322.34066248</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>144063.479</t>
+          <t>2705927.70396172</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>131512.9</t>
+          <t>2473218.33201866</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>127875.975</t>
+          <t>2251829.38971421</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>135502.753</t>
+          <t>2522696.35008506</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>144432.419</t>
+          <t>2675664.46797961</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>143535.48</t>
+          <t>2341509.78794984</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>137423.751</t>
+          <t>2211861.0252521</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>141230.215</t>
+          <t>2362881.4347047</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>149285.336</t>
+          <t>2558230.46020092</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>148647.785</t>
+          <t>2536580.45629792</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>146452.754</t>
+          <t>2437547.78207593</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>136295.829</t>
+          <t>2439014.46378651</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>133850.967</t>
+          <t>2711916.13868508</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>130875.075</t>
+          <t>2756086.66383692</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>21289271.5883617</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>121.64</t>
+          <t>18315178.6879104</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>144.67</t>
+          <t>16233901.8565931</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>150.4</t>
+          <t>14761559.2202773</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>16628739.7894945</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>125.34</t>
+          <t>17169878.1278504</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>128.54</t>
+          <t>14986316.6725713</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>136.73</t>
+          <t>14367934.1551703</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>134.64</t>
+          <t>15445118.637219</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>124.07</t>
+          <t>16527248.3586938</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>123.6</t>
+          <t>16431446.4708916</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>133.08</t>
+          <t>15695785.5143952</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>151.56</t>
+          <t>15670296.4921833</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>149.96</t>
+          <t>18261131.6571798</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>136.09</t>
+          <t>19296059.8571648</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3161322.34066248</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>3162003.21704048</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3190264.114627</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.626</t>
+          <t>3132792.50756439</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.488</t>
+          <t>3111508.39892445</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.441</t>
+          <t>3175021.90317712</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.779</t>
+          <t>3177330.7508373</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.848</t>
+          <t>3158907.6323282</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.732</t>
+          <t>3202549.61161134</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.599</t>
+          <t>3293486.32002534</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.583</t>
+          <t>3402767.23963482</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.724</t>
+          <t>3502464.42346657</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.609</t>
+          <t>3608715.10270966</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>3568185.74207821</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.203</t>
+          <t>3228363.12701674</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2745397.56350226</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2751518.43333455</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2779033.86443456</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2738093.4749526</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2724023.03041981</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2798438.82226227</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2811371.36632261</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2795791.87458553</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2843017.58644692</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2936298.47565236</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3028408.70367268</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3144687.39563941</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>3243967.67620102</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>3209106.84218701</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2900728.67846221</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2078299.96576752</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1901180.23991828</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1754035.34089134</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1596193.64916579</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1830467.94952494</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1961397.30866039</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1706866.62576016</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1674573.2976679</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1836433.0757053</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1996314.27248908</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1991628.47575208</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1871575.23564407</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1871692.7449635</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2071920.44080321</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2154265.81226498</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>312098757701.117</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>319298673481.342</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>321778315605.456</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>320196402983.616</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>317216015719.813</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>325459273541.27</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>328030507924.08</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>325323564853.173</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>331379488395.548</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>334499233548.775</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>332380294771.953</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>341349774818.964</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>342869261420.213</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>334576527346.378</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>308976947775.952</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>382726006448.701</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>389284549228.69</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>391676125901.014</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>388633925677.604</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>383923988139.899</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>389925327579.717</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>392107376070.73</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>387820539800.315</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>393525191645.974</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>396059820600.167</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>393133471820.06</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>398136071209.141</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>399710537203.396</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>390385670608.185</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>360330389354.384</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>190758977119.138</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>192679471799.875</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>193425836607.363</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>188628700287.614</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>186004813094.526</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>187362767818.476</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>186611470588.726</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>182923853872.446</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>184383598099.934</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>184725000370.948</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>182234550312.68</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>183318047859.215</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>183649140927.156</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>177499233185.077</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>164343253375.303</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>66857749.2126289</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>66906725.9645875</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>67373676.3052891</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>66579630.0285745</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>65663597.6201838</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>65252580.5313763</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>64759579.8985275</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>63747574.9491338</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>63536567.4245277</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>63676553.3755598</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>63916550.6509646</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>64197437.9942584</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>64438263.1188283</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>63045011.7904479</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>58129224.001234</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>53766608.2829578</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>54251580.7304874</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>54766801.4608104</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>54303584.0121397</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>53698651.5500802</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>53778208.9583263</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>53800176.4988066</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>53220101.5929844</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>53164769.1708257</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>53333460.660155</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>53676055.1024794</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>54500985.1639254</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>54736152.7603184</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>53522793.7423068</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>49343702.106554</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>128222471703.372</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>128765062457.942</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>127817186581.938</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>124807729306.285</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>121678752876.065</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>121538020243.119</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>120328063648.719</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>117808290223.311</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>117674143014.12</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>117553502189.724</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>115915216876.385</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>117204754014.252</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>117623105374.446</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>114963431160.589</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>105856420383.388</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>102785336309.266</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>103927217679.788</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>103369217150.21</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>101246988677.691</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>99076807477.4328</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>100177904290.721</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>99460607407.5732</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>97626583840.2885</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>97944352454.1957</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>98147153379.7101</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>96831355076.2254</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>99350695264.1884</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>99761612250.3796</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>97421377310.7341</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>89716477994.8995</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.230758021741052</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.238337633636048</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.241076805747217</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.251387734325517</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.256340884219462</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.260870477022473</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.271140539201546</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.285334184329508</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.286944809377974</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.290876712969125</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292023635945964</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.582530546331134</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.586060041193847</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.590377919030962</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.591940917362233</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.595380718738523</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.598079257768512</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.598630257895856</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.591938496678375</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.598516075120748</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.596621977659668</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.595962081413037</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.158140003356385</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.147030896598676</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.139973846650393</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.128099919740821</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.119706968470586</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.112478836637586</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.10165777433117</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0941558904206893</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0859676869298493</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0839298807997789</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0834428540695712</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.355259208929566</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.362489266994182</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.368229777671674</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.378964815710906</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.387284294641542</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.392477077482147</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.403755074305688</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.415452544482424</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.416934961034728</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.419814950813904</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.418894617770864</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.418894617770864</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.418894617770864</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.418894617770864</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.418894617770864</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.550174601269312</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.547905426901681</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.546352186369959</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.54110409995312</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.537348790411007</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.535359845367898</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.528875058149679</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.520061514850739</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.522272050510547</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.519671129621698</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.520469255699721</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.520469255699721</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.520469255699721</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.520469255699721</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.520469255699721</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0659947612296941</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0610338775327082</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0568466073869387</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0513596557645451</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0467954863760222</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0435916485785263</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0387984389732046</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0359145120954092</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0322215598832963</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.03194249099297</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0320646979579868</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0320646979579868</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0320646979579868</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0320646979579868</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0320646979579868</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>9871402.09181</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8653218.418</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>7988888.18361</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7179054.14357</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8074125.72561</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>8689624.72806</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7611125.04837</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7256470.83011</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>7844053.41652</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8567572.2029</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>8631934.89718</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>8376839.74448</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>8489190.97734</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>9695796.51719</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>9388243.2637</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>5239622.30643</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4607107.94388</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>4227253.67291</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3848023.03888</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>4353164.29961</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4637061.77664</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4048376.41371</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3886434.32292</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4199314.51041</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4554544.73269</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>4528208.93205</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>4309123.01772</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>4310707.20875</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>4785564.42746</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>4915208.0621</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1989651471.99018</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1983884302.2851</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1980909167.36731</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1976859801.86027</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1968606741.73799</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1962344651.4736</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1959208836.15363</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1965164273.02802</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1965416581.54312</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1969463696.72909</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1977047990.64659</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1984685690.04331</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1991084750.73126</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1994399618.16927</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1979901624.26518</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
